--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B4" t="n">
         <v>79089</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R4" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B5" t="n">
         <v>79089</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R5" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R10" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R11" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>91860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R4" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R5" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128793132</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128793125</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128793137</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B4" t="n">
         <v>79116</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R4" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B5" t="n">
         <v>79116</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R5" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>91494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R6" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R7" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128793125</v>
+        <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748643</v>
+        <v>748825</v>
       </c>
       <c r="R8" t="n">
-        <v>7162552</v>
+        <v>7162234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793137</v>
+        <v>128793125</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>57876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748825</v>
+        <v>748643</v>
       </c>
       <c r="R9" t="n">
-        <v>7162234</v>
+        <v>7162552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91860</v>
+        <v>91865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793130</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793131</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B6" t="n">
-        <v>91494</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R6" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>91499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R7" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B10" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R10" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R11" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91865</v>
+        <v>91870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128793137</v>
+        <v>128793125</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>57876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748825</v>
+        <v>748643</v>
       </c>
       <c r="R8" t="n">
-        <v>7162234</v>
+        <v>7162552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793125</v>
+        <v>128793137</v>
       </c>
       <c r="B9" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748643</v>
+        <v>748825</v>
       </c>
       <c r="R9" t="n">
-        <v>7162552</v>
+        <v>7162234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>128793154</v>
       </c>
       <c r="B11" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R6" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R7" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128793125</v>
+        <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748643</v>
+        <v>748825</v>
       </c>
       <c r="R8" t="n">
-        <v>7162552</v>
+        <v>7162234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793137</v>
+        <v>128793125</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>57876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748825</v>
+        <v>748643</v>
       </c>
       <c r="R9" t="n">
-        <v>7162234</v>
+        <v>7162552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1934,6 +1934,862 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128918336</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>748799</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7162259</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128918277</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>748799</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7162259</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128918439</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57876</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>748592</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7162684</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>observerad på ca 3 meters håll</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128918390</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91469</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>748767</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7162369</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128918580</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>748872</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7162562</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128918270</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>748801</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7162220</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128918457</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>748755</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7162653</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128918545</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>748837</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7162624</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>äldre hack i granlåga</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R6" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R7" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R10" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R11" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128918336</v>
+        <v>128918277</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,31 +1947,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2017,17 +2016,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2046,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128918277</v>
+        <v>128918336</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,30 +2052,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2126,13 +2122,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2257,41 +2257,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B18" t="n">
-        <v>91469</v>
+        <v>57713</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2299,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R18" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,13 +2338,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2362,42 +2367,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>91469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2405,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R19" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,17 +2447,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91870</v>
+        <v>91874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793130</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793131</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128793132</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128793125</v>
       </c>
       <c r="B9" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128918277</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>128918336</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>128918439</v>
       </c>
       <c r="B17" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,42 +2257,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>57713</v>
+        <v>91473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2300,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R18" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,17 +2337,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2367,41 +2362,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B19" t="n">
-        <v>91469</v>
+        <v>57717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R19" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,13 +2443,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>128918270</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128918545</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B4" t="n">
         <v>79124</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R4" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B5" t="n">
         <v>79124</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R5" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R6" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B7" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R7" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2257,41 +2257,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B18" t="n">
-        <v>91473</v>
+        <v>57717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2299,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R18" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,13 +2338,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2362,42 +2367,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>91473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2405,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R19" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,17 +2447,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B4" t="n">
         <v>79124</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R4" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B5" t="n">
         <v>79124</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R5" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2257,42 +2257,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>91473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2300,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R18" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,17 +2337,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2367,41 +2362,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B19" t="n">
-        <v>91473</v>
+        <v>57717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R19" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,13 +2443,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91874</v>
+        <v>91879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793130</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793131</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128793132</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128793125</v>
       </c>
       <c r="B9" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128918277</v>
+        <v>128918336</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,30 +1947,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2016,13 +2017,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2041,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128918336</v>
+        <v>128918277</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2052,31 +2057,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2122,17 +2126,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>128918439</v>
       </c>
       <c r="B17" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,41 +2257,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B18" t="n">
-        <v>91473</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2299,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R18" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,13 +2338,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2362,42 +2367,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>91478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2405,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R19" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,17 +2447,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>128918270</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128918545</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91887</v>
+        <v>91890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B4" t="n">
         <v>79034</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R4" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B5" t="n">
         <v>79034</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R5" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B6" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R6" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R7" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128918336</v>
+        <v>128918277</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,31 +1947,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2017,17 +2016,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2046,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128918277</v>
+        <v>128918336</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,30 +2052,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2126,13 +2122,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2257,42 +2257,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>91488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2300,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R18" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,17 +2337,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2367,41 +2362,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B19" t="n">
-        <v>91485</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R19" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,13 +2443,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91890</v>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R4" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R5" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128793132</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128793137</v>
+        <v>128793125</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748825</v>
+        <v>748643</v>
       </c>
       <c r="R8" t="n">
-        <v>7162234</v>
+        <v>7162552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793125</v>
+        <v>128793137</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748643</v>
+        <v>748825</v>
       </c>
       <c r="R9" t="n">
-        <v>7162552</v>
+        <v>7162234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B10" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R10" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R11" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128918277</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128918270</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R4" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R5" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R6" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R7" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R10" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R11" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2257,41 +2257,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B18" t="n">
-        <v>91491</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2299,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R18" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,13 +2338,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2362,42 +2367,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>91491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2405,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R19" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,17 +2447,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R4" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R5" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128793125</v>
+        <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748643</v>
+        <v>748825</v>
       </c>
       <c r="R8" t="n">
-        <v>7162552</v>
+        <v>7162234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793137</v>
+        <v>128793125</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748825</v>
+        <v>748643</v>
       </c>
       <c r="R9" t="n">
-        <v>7162234</v>
+        <v>7162552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B10" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R10" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R11" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128918277</v>
+        <v>128918336</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,30 +1947,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2016,13 +2017,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2041,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128918336</v>
+        <v>128918277</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2052,31 +2057,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2122,17 +2126,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2257,42 +2257,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>91491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2300,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R18" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,17 +2337,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2367,41 +2362,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B19" t="n">
-        <v>91491</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R19" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,13 +2443,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91893</v>
+        <v>91900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793130</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793131</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128793132</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128793125</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>91551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R10" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R11" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128918336</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>128918277</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>128918439</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,41 +2257,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B18" t="n">
-        <v>91491</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2299,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R18" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,13 +2338,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2362,42 +2367,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>91497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2405,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R19" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,17 +2447,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>128918270</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128918545</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2257,42 +2257,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>91497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2300,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R18" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,17 +2337,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2367,41 +2362,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B19" t="n">
-        <v>91497</v>
+        <v>57722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R19" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,13 +2443,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91900</v>
+        <v>91907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B4" t="n">
         <v>79039</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R4" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B5" t="n">
         <v>79039</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R5" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91907</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793131</v>
+        <v>128793130</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748357</v>
+        <v>748784</v>
       </c>
       <c r="R4" t="n">
-        <v>7162840</v>
+        <v>7162268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793130</v>
+        <v>128793131</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748784</v>
+        <v>748357</v>
       </c>
       <c r="R5" t="n">
-        <v>7162268</v>
+        <v>7162840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128793132</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128793125</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128918336</v>
+        <v>128918277</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,31 +1947,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2017,17 +2016,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2046,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128918277</v>
+        <v>128918336</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,30 +2052,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2126,13 +2122,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>128918439</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>128918580</v>
       </c>
       <c r="B19" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128918270</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128918545</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R6" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R7" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128793137</v>
+        <v>128793125</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748825</v>
+        <v>748643</v>
       </c>
       <c r="R8" t="n">
-        <v>7162234</v>
+        <v>7162552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793125</v>
+        <v>128793137</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748643</v>
+        <v>748825</v>
       </c>
       <c r="R9" t="n">
-        <v>7162552</v>
+        <v>7162234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B10" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R10" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R11" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128793125</v>
+        <v>128793137</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748643</v>
+        <v>748825</v>
       </c>
       <c r="R8" t="n">
-        <v>7162552</v>
+        <v>7162234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793137</v>
+        <v>128793125</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748825</v>
+        <v>748643</v>
       </c>
       <c r="R9" t="n">
-        <v>7162234</v>
+        <v>7162552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793153</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793128</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793132</v>
+        <v>128793124</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748353</v>
+        <v>748397</v>
       </c>
       <c r="R6" t="n">
-        <v>7162801</v>
+        <v>7162811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793124</v>
+        <v>128793132</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748397</v>
+        <v>748353</v>
       </c>
       <c r="R7" t="n">
-        <v>7162811</v>
+        <v>7162801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128793137</v>
+        <v>128793125</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748825</v>
+        <v>748643</v>
       </c>
       <c r="R8" t="n">
-        <v>7162234</v>
+        <v>7162552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128793125</v>
+        <v>128793137</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748643</v>
+        <v>748825</v>
       </c>
       <c r="R9" t="n">
-        <v>7162552</v>
+        <v>7162234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128793136</v>
+        <v>128793154</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storbrännet, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748556</v>
+        <v>748802</v>
       </c>
       <c r="R10" t="n">
-        <v>7162654</v>
+        <v>7162656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128793154</v>
+        <v>128793136</v>
       </c>
       <c r="B11" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Storbrännet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748802</v>
+        <v>748556</v>
       </c>
       <c r="R11" t="n">
-        <v>7162656</v>
+        <v>7162654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>128793127</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128793129</v>
       </c>
       <c r="B13" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128793122</v>
       </c>
       <c r="B14" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2257,41 +2257,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2299,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R18" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,13 +2338,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2362,42 +2367,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2405,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R19" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,17 +2447,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2597,14 +2597,10 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -1939,7 +1939,7 @@
         <v>128918277</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,42 +2257,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>91507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2300,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R18" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,17 +2337,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2367,41 +2362,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B19" t="n">
-        <v>91504</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R19" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2447,13 +2443,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>128918270</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -1939,7 +1939,7 @@
         <v>128918277</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,41 +2257,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128918390</v>
+        <v>128918580</v>
       </c>
       <c r="B18" t="n">
-        <v>91507</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2299,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>748767</v>
+        <v>748872</v>
       </c>
       <c r="R18" t="n">
-        <v>7162369</v>
+        <v>7162562</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,13 +2338,17 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2362,42 +2367,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128918580</v>
+        <v>128918390</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>91509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2405,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>748872</v>
+        <v>748767</v>
       </c>
       <c r="R19" t="n">
-        <v>7162562</v>
+        <v>7162369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,17 +2447,13 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>äldre hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>128918270</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2370,7 +2370,7 @@
         <v>128918390</v>
       </c>
       <c r="B19" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>128918457</v>
       </c>
       <c r="B21" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2786,6 +2786,872 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129633100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>748813</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7162218</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129633035</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>748795</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7162324</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129633089</v>
+      </c>
+      <c r="B25" t="n">
+        <v>82878</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>748799</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7162285</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på stammen av en död gammal gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129633080</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>748795</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7162316</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129632943</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>748639</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7162594</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129633094</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>748828</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7162245</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129633087</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>748777</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7162299</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129632989</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>748657</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7162585</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2898,10 +2898,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129633035</v>
+        <v>129633089</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,27 +2909,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>748795</v>
+        <v>748799</v>
       </c>
       <c r="R24" t="n">
-        <v>7162324</v>
+        <v>7162285</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,6 +2976,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,10 +3008,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129633089</v>
+        <v>129633035</v>
       </c>
       <c r="B25" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3014,27 +3019,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3045,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>748799</v>
+        <v>748795</v>
       </c>
       <c r="R25" t="n">
-        <v>7162285</v>
+        <v>7162324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3081,11 +3086,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -3218,42 +3218,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129632943</v>
+        <v>129633094</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>748639</v>
+        <v>748828</v>
       </c>
       <c r="R27" t="n">
-        <v>7162594</v>
+        <v>7162245</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3310,7 +3310,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3329,42 +3328,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129633094</v>
+        <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>748828</v>
+        <v>748639</v>
       </c>
       <c r="R28" t="n">
-        <v>7162245</v>
+        <v>7162594</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,7 +3411,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3421,6 +3420,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2791,7 +2791,7 @@
         <v>129633100</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>129633089</v>
       </c>
       <c r="B24" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>129633035</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>129633080</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129633094</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>129633087</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>129632989</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2791,7 +2791,7 @@
         <v>129633100</v>
       </c>
       <c r="B23" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>129633089</v>
       </c>
       <c r="B24" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>129633035</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>129633080</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3218,42 +3218,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129633094</v>
+        <v>129632943</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>748828</v>
+        <v>748639</v>
       </c>
       <c r="R27" t="n">
-        <v>7162245</v>
+        <v>7162594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3310,6 +3310,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3328,42 +3329,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129632943</v>
+        <v>129633094</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3371,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>748639</v>
+        <v>748828</v>
       </c>
       <c r="R28" t="n">
-        <v>7162594</v>
+        <v>7162245</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,7 +3412,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3420,7 +3421,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>129633087</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>129632989</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2791,7 +2791,7 @@
         <v>129633100</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>129633089</v>
       </c>
       <c r="B24" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>129633035</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>129633080</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3218,42 +3218,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129632943</v>
+        <v>129633094</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>748639</v>
+        <v>748828</v>
       </c>
       <c r="R27" t="n">
-        <v>7162594</v>
+        <v>7162245</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3310,7 +3310,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3329,42 +3328,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129633094</v>
+        <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>748828</v>
+        <v>748639</v>
       </c>
       <c r="R28" t="n">
-        <v>7162245</v>
+        <v>7162594</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,7 +3411,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3421,6 +3420,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>129633087</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>129632989</v>
       </c>
       <c r="B30" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2901,7 +2901,7 @@
         <v>129633089</v>
       </c>
       <c r="B24" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>129633035</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>129633080</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>129633087</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2898,10 +2898,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129633089</v>
+        <v>129633035</v>
       </c>
       <c r="B24" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,27 +2909,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>748799</v>
+        <v>748795</v>
       </c>
       <c r="R24" t="n">
-        <v>7162285</v>
+        <v>7162324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,11 +2976,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3008,10 +3003,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129633035</v>
+        <v>129633089</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3019,27 +3014,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3050,10 +3045,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>748795</v>
+        <v>748799</v>
       </c>
       <c r="R25" t="n">
-        <v>7162324</v>
+        <v>7162285</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,6 +3081,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2898,10 +2898,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129633035</v>
+        <v>129633089</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,27 +2909,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>748795</v>
+        <v>748799</v>
       </c>
       <c r="R24" t="n">
-        <v>7162324</v>
+        <v>7162285</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,6 +2976,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,10 +3008,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129633089</v>
+        <v>129633035</v>
       </c>
       <c r="B25" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3014,27 +3019,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3045,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>748799</v>
+        <v>748795</v>
       </c>
       <c r="R25" t="n">
-        <v>7162285</v>
+        <v>7162324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3081,11 +3086,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -3331,7 +3331,7 @@
         <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2898,10 +2898,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129633089</v>
+        <v>129633035</v>
       </c>
       <c r="B24" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,27 +2909,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>748799</v>
+        <v>748795</v>
       </c>
       <c r="R24" t="n">
-        <v>7162285</v>
+        <v>7162324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,11 +2976,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3008,10 +3003,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129633035</v>
+        <v>129633089</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3019,27 +3014,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3050,10 +3045,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>748795</v>
+        <v>748799</v>
       </c>
       <c r="R25" t="n">
-        <v>7162324</v>
+        <v>7162285</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,6 +3081,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3331,7 +3331,7 @@
         <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -3331,7 +3331,7 @@
         <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2791,7 +2791,7 @@
         <v>129633100</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>129633035</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>129633089</v>
       </c>
       <c r="B25" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>129633080</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3218,42 +3218,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129633094</v>
+        <v>129632943</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>748828</v>
+        <v>748639</v>
       </c>
       <c r="R27" t="n">
-        <v>7162245</v>
+        <v>7162594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3310,6 +3310,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3328,42 +3329,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129632943</v>
+        <v>129633094</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>57734</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3371,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>748639</v>
+        <v>748828</v>
       </c>
       <c r="R28" t="n">
-        <v>7162594</v>
+        <v>7162245</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,7 +3412,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3420,7 +3421,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>129633087</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>129632989</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2791,7 +2791,7 @@
         <v>129633100</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129633035</v>
+        <v>129633089</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>82924</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,27 +2909,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>748795</v>
+        <v>748799</v>
       </c>
       <c r="R24" t="n">
-        <v>7162324</v>
+        <v>7162285</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,6 +2976,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,10 +3008,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129633089</v>
+        <v>129633035</v>
       </c>
       <c r="B25" t="n">
-        <v>82921</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3014,27 +3019,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3045,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>748799</v>
+        <v>748795</v>
       </c>
       <c r="R25" t="n">
-        <v>7162285</v>
+        <v>7162324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3081,11 +3086,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på stammen av en död gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3116,7 +3116,7 @@
         <v>129633080</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3218,42 +3218,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129632943</v>
+        <v>129633094</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>748639</v>
+        <v>748828</v>
       </c>
       <c r="R27" t="n">
-        <v>7162594</v>
+        <v>7162245</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3310,7 +3310,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3329,42 +3328,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129633094</v>
+        <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>748828</v>
+        <v>748639</v>
       </c>
       <c r="R28" t="n">
-        <v>7162245</v>
+        <v>7162594</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3412,7 +3411,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3421,6 +3420,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>129633087</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>129632989</v>
       </c>
       <c r="B30" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2901,7 +2901,7 @@
         <v>129633089</v>
       </c>
       <c r="B24" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>129633035</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>129633080</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>129632943</v>
       </c>
       <c r="B28" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>129633087</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46526-2025 artfynd.xlsx
+++ b/artfynd/A 46526-2025 artfynd.xlsx
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
